--- a/artfynd/A 60004-2021 artfynd.xlsx
+++ b/artfynd/A 60004-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 60004-2021 artfynd.xlsx
+++ b/artfynd/A 60004-2021 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>98822751</v>
+        <v>96276250</v>
       </c>
       <c r="B2" t="n">
-        <v>86196</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99024</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,41 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4405</v>
+        <v>504</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Diskvaxskivling</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hygrophorus discoideus</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Pers.) Fr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Edsforsen, Jmt</t>
+          <t>Edesforsen, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>486652.2746632514</v>
+        <v>486859</v>
       </c>
       <c r="R2" t="n">
-        <v>7049876.399458967</v>
+        <v>7049993</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +744,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-10-06</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-24</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-10-06</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-24</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -769,33 +758,29 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Sebastian Acker</t>
+          <t>Erik Söderhjelm</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Sebastian Acker</t>
+          <t>Erik Söderhjelm</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>98822752</v>
+        <v>98822747</v>
       </c>
       <c r="B3" t="n">
-        <v>90319</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99024</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,21 +788,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4769</v>
+        <v>504</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>486704.9829684552</v>
+        <v>486690</v>
       </c>
       <c r="R3" t="n">
-        <v>7049894.886442897</v>
+        <v>7050049</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -860,19 +845,9 @@
           <t>2021-10-06</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-10-06</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,37 +874,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>98822745</v>
+        <v>98822749</v>
       </c>
       <c r="B4" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>486762.7558887944</v>
+        <v>486699</v>
       </c>
       <c r="R4" t="n">
-        <v>7050058.558351527</v>
+        <v>7049960</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -972,19 +942,9 @@
           <t>2021-10-06</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2021-10-06</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,37 +971,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>98822749</v>
+        <v>98822751</v>
       </c>
       <c r="B5" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89143</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>4405</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Diskvaxskivling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hygrophorus discoideus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.) Fr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>486699.011069518</v>
+        <v>486652</v>
       </c>
       <c r="R5" t="n">
-        <v>7049959.943232134</v>
+        <v>7049876</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1084,19 +1039,9 @@
           <t>2021-10-06</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2021-10-06</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,15 +1068,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>98822750</v>
+        <v>98822752</v>
       </c>
       <c r="B6" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92869</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1139,21 +1079,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222498</v>
+        <v>4769</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>486674.9716282383</v>
+        <v>486705</v>
       </c>
       <c r="R6" t="n">
-        <v>7049970.734014129</v>
+        <v>7049895</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1196,19 +1136,9 @@
           <t>2021-10-06</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2021-10-06</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,37 +1165,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>98822748</v>
+        <v>98822745</v>
       </c>
       <c r="B7" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>486677.0452110192</v>
+        <v>486763</v>
       </c>
       <c r="R7" t="n">
-        <v>7050039.764232339</v>
+        <v>7050059</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1308,19 +1233,9 @@
           <t>2021-10-06</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2021-10-06</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,15 +1262,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>98822747</v>
+        <v>98822748</v>
       </c>
       <c r="B8" t="n">
-        <v>96239</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1363,21 +1273,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>504</v>
+        <v>222498</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1387,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>486690.0182321656</v>
+        <v>486677</v>
       </c>
       <c r="R8" t="n">
-        <v>7050049.063389673</v>
+        <v>7050040</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1420,19 +1330,9 @@
           <t>2021-10-06</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2021-10-06</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1459,15 +1359,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>96276250</v>
+        <v>98822750</v>
       </c>
       <c r="B9" t="n">
-        <v>96239</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1475,41 +1370,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>504</v>
+        <v>222498</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Edesforsen, Jmt</t>
+          <t>Edsforsen, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>486858.3750096392</v>
+        <v>486675</v>
       </c>
       <c r="R9" t="n">
-        <v>7049993.13155406</v>
+        <v>7049971</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1533,22 +1424,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2021-09-24</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-06</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2021-09-24</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-06</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1557,19 +1438,18 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Erik Söderhjelm</t>
+          <t>Sebastian Acker</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Erik Söderhjelm</t>
+          <t>Sebastian Acker</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>

--- a/artfynd/A 60004-2021 artfynd.xlsx
+++ b/artfynd/A 60004-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96276250</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -871,6 +881,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98822747</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -968,6 +983,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98822749</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1065,6 +1085,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98822751</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1162,6 +1187,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98822752</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1259,6 +1289,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98822745</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1356,6 +1391,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98822748</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1453,8 +1493,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98822750</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>